--- a/artfynd/A 22555-2025 artfynd.xlsx
+++ b/artfynd/A 22555-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74027552</v>
       </c>
       <c r="B2" t="n">
-        <v>104790</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442247.9077555669</v>
+        <v>442248</v>
       </c>
       <c r="R2" t="n">
-        <v>6398348.18205905</v>
+        <v>6398348</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1979-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1979-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74153167</v>
       </c>
       <c r="B3" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442247.9077555669</v>
+        <v>442248</v>
       </c>
       <c r="R3" t="n">
-        <v>6398348.18205905</v>
+        <v>6398348</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -870,19 +850,9 @@
           <t>1979-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1979-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -926,12 +896,7 @@
         <v>74531784</v>
       </c>
       <c r="B4" t="n">
-        <v>96820</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442247.9077555669</v>
+        <v>442248</v>
       </c>
       <c r="R4" t="n">
-        <v>6398348.18205905</v>
+        <v>6398348</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -996,19 +961,9 @@
           <t>1979-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1979-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1052,12 +1007,7 @@
         <v>74601610</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442247.9077555669</v>
+        <v>442248</v>
       </c>
       <c r="R5" t="n">
-        <v>6398348.18205905</v>
+        <v>6398348</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1122,19 +1072,9 @@
           <t>1979-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1979-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 22555-2025 artfynd.xlsx
+++ b/artfynd/A 22555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74027552</v>
       </c>
       <c r="B2" t="n">
-        <v>107245</v>
+        <v>107254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74153167</v>
       </c>
       <c r="B3" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74531784</v>
       </c>
       <c r="B4" t="n">
-        <v>99108</v>
+        <v>99113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22555-2025 artfynd.xlsx
+++ b/artfynd/A 22555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74027552</v>
       </c>
       <c r="B2" t="n">
-        <v>107254</v>
+        <v>107259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74153167</v>
       </c>
       <c r="B3" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74531784</v>
       </c>
       <c r="B4" t="n">
-        <v>99113</v>
+        <v>99114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>74601610</v>
       </c>
       <c r="B5" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22555-2025 artfynd.xlsx
+++ b/artfynd/A 22555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74027552</v>
       </c>
       <c r="B2" t="n">
-        <v>107259</v>
+        <v>107287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74153167</v>
       </c>
       <c r="B3" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74531784</v>
       </c>
       <c r="B4" t="n">
-        <v>99114</v>
+        <v>99141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>74601610</v>
       </c>
       <c r="B5" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22555-2025 artfynd.xlsx
+++ b/artfynd/A 22555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74027552</v>
       </c>
       <c r="B2" t="n">
-        <v>107287</v>
+        <v>107293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74153167</v>
       </c>
       <c r="B3" t="n">
-        <v>98539</v>
+        <v>98545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74531784</v>
       </c>
       <c r="B4" t="n">
-        <v>99141</v>
+        <v>99147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>74601610</v>
       </c>
       <c r="B5" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22555-2025 artfynd.xlsx
+++ b/artfynd/A 22555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74027552</v>
       </c>
       <c r="B2" t="n">
-        <v>107293</v>
+        <v>107300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74153167</v>
       </c>
       <c r="B3" t="n">
-        <v>98545</v>
+        <v>98552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74531784</v>
       </c>
       <c r="B4" t="n">
-        <v>99147</v>
+        <v>99154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>74601610</v>
       </c>
       <c r="B5" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22555-2025 artfynd.xlsx
+++ b/artfynd/A 22555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74027552</v>
       </c>
       <c r="B2" t="n">
-        <v>107300</v>
+        <v>107304</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74153167</v>
       </c>
       <c r="B3" t="n">
-        <v>98552</v>
+        <v>98556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74531784</v>
       </c>
       <c r="B4" t="n">
-        <v>99154</v>
+        <v>99158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>74601610</v>
       </c>
       <c r="B5" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22555-2025 artfynd.xlsx
+++ b/artfynd/A 22555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74027552</v>
       </c>
       <c r="B2" t="n">
-        <v>107304</v>
+        <v>107312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74153167</v>
       </c>
       <c r="B3" t="n">
-        <v>98556</v>
+        <v>98563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74531784</v>
       </c>
       <c r="B4" t="n">
-        <v>99158</v>
+        <v>99165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>74601610</v>
       </c>
       <c r="B5" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22555-2025 artfynd.xlsx
+++ b/artfynd/A 22555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74027552</v>
       </c>
       <c r="B2" t="n">
-        <v>107315</v>
+        <v>107320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74153167</v>
       </c>
       <c r="B3" t="n">
-        <v>98566</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74531784</v>
       </c>
       <c r="B4" t="n">
-        <v>99168</v>
+        <v>99173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>74601610</v>
       </c>
       <c r="B5" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22555-2025 artfynd.xlsx
+++ b/artfynd/A 22555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74027552</v>
       </c>
       <c r="B2" t="n">
-        <v>107320</v>
+        <v>107328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74153167</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74531784</v>
       </c>
       <c r="B4" t="n">
-        <v>99173</v>
+        <v>99181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>74601610</v>
       </c>
       <c r="B5" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22555-2025 artfynd.xlsx
+++ b/artfynd/A 22555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74027552</v>
       </c>
       <c r="B2" t="n">
-        <v>107328</v>
+        <v>107338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74153167</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>74531784</v>
       </c>
       <c r="B4" t="n">
-        <v>99181</v>
+        <v>99191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>74601610</v>
       </c>
       <c r="B5" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22555-2025 artfynd.xlsx
+++ b/artfynd/A 22555-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>74027552</v>
       </c>
       <c r="B2" t="n">
-        <v>107338</v>
+        <v>107867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74153167</v>
+        <v>74601610</v>
       </c>
       <c r="B3" t="n">
-        <v>98589</v>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,19 +797,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -857,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7D0i 1242. SOM: Dactylorhiza maculata ssp. maculata. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 7D0i 1242. SOM: Lycopodium annotinum. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74531784</v>
+        <v>74782120</v>
       </c>
       <c r="B4" t="n">
-        <v>99191</v>
+        <v>102559</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,16 +908,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222541</v>
+        <v>222133</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Juncus squarrosus</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -968,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7D0i 1242. SOM: Juncus squarrosus. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 7D0i 1242. SOM: Polygala vulgaris. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,27 +1008,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74601610</v>
+        <v>74531784</v>
       </c>
       <c r="B5" t="n">
-        <v>97540</v>
+        <v>99646</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>222541</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Juncus squarrosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1079,7 +1083,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7D0i 1242. SOM: Lycopodium annotinum. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 7D0i 1242. SOM: Juncus squarrosus. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,6 +1112,113 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>74153167</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Jäbo. 300m O Jäbo.Gärdesberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>442248</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6398348</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sandseryd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1979-01-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1979-12-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7D0i 1242. SOM: Dactylorhiza maculata ssp. maculata. LEG: Roland Carlsson</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrskog, myrmark, vägren, åkerren</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 22555-2025 artfynd.xlsx
+++ b/artfynd/A 22555-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74027552</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74601610</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74782120</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74531784</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,8 +1248,20 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74153167</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>